--- a/BehaviourChangeTechniques/BCIO-bcto-hierarchy.xlsx
+++ b/BehaviourChangeTechniques/BCIO-bcto-hierarchy.xlsx
@@ -572,7 +572,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
